--- a/data/degradation/task_spectrum_template.xlsx
+++ b/data/degradation/task_spectrum_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,11 @@
       <c r="O1" t="inlineStr">
         <is>
           <t>oil_temperature_c</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>seconds_per_degree</t>
         </is>
       </c>
     </row>
